--- a/Car_Circuitry/Car_Circuitry_BOM.xlsx
+++ b/Car_Circuitry/Car_Circuitry_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oasis\Documents\School\Assignments\Undergraduate Year 5\Chem-E Car Team\McMaster_Chem-E_Car_25-26\Car_Circuitry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72B925FD-C9F2-4550-AA5A-00320BBD05EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43BB5D52-D585-4A05-BF61-5680B2F02445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13620" xr2:uid="{EA864D17-A2FA-4459-BC44-DC5D03B4B2F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13620" xr2:uid="{57EE16C2-1588-46C7-AC60-D32C9E3DA668}"/>
   </bookViews>
   <sheets>
     <sheet name="Car_Circuitry_BOM" sheetId="1" r:id="rId1"/>
@@ -305,7 +305,7 @@
     <t>RCWE0805R100FKEA</t>
   </si>
   <si>
-    <t>390 Ω</t>
+    <t>400 Ω</t>
   </si>
   <si>
     <t>R2, R3</t>
@@ -353,7 +353,7 @@
     <t>ERA-6AEB204V</t>
   </si>
   <si>
-    <t>320 Ω</t>
+    <t>330 Ω</t>
   </si>
   <si>
     <t>R9</t>
@@ -818,7 +818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8C1EFA-50FD-475B-9A22-9E84E72D5A67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCEFBE8D-C481-435D-9AF0-F3D6748809DF}">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/Car_Circuitry/Car_Circuitry_BOM.xlsx
+++ b/Car_Circuitry/Car_Circuitry_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oasis\Documents\School\Assignments\Undergraduate Year 4\Chem-E Car Team\McMaster_Chem-E_Car_24-25\Car_Circuitry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oasis\Documents\School\Assignments\Undergraduate Year 5\Chem-E Car Team\McMaster_Chem-E_Car_25-26\Car_Circuitry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93615B8E-6D8F-43D1-B40E-494881BD6175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43BB5D52-D585-4A05-BF61-5680B2F02445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13620" xr2:uid="{E830964A-B488-45D9-84B5-630F87D382AA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13620" xr2:uid="{57EE16C2-1588-46C7-AC60-D32C9E3DA668}"/>
   </bookViews>
   <sheets>
     <sheet name="Car_Circuitry_BOM" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="128">
   <si>
     <t>Comment</t>
   </si>
@@ -59,19 +59,37 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>TPS552892RYQR</t>
+    <t>REF2033QDDCRQ1</t>
   </si>
   <si>
     <t>Integrated Circuit</t>
   </si>
   <si>
-    <t>BOOST1</t>
+    <t>AREF</t>
+  </si>
+  <si>
+    <t>SOT95P280X110-5N</t>
+  </si>
+  <si>
+    <t>B2B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 2POS 2.5MM</t>
+  </si>
+  <si>
+    <t>AUXM, DRVM, LEDB, PROP, SPKR, STRM, SW, TRB</t>
+  </si>
+  <si>
+    <t>FP-B2B-XH-A_LF_SN-MFG</t>
+  </si>
+  <si>
+    <t>CMP-2000-05888-3</t>
   </si>
   <si>
     <t>TPS61023DRLT</t>
   </si>
   <si>
-    <t>BOOST2</t>
+    <t>BOOST</t>
   </si>
   <si>
     <t>SOTFL50P160X60-6N</t>
@@ -83,7 +101,7 @@
     <t>Capacitor</t>
   </si>
   <si>
-    <t>C1, C2</t>
+    <t>C1, C4, C5, C8, C9, C13</t>
   </si>
   <si>
     <t>CAPC2012X95N</t>
@@ -95,7 +113,7 @@
     <t>10 μF</t>
   </si>
   <si>
-    <t>C3, C4, C19</t>
+    <t>C2, C6, C14</t>
   </si>
   <si>
     <t>CAPC2012X140N</t>
@@ -104,85 +122,58 @@
     <t>CL21B106KOQNNNE</t>
   </si>
   <si>
-    <t>82 nF</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>CAPC1005X55N</t>
-  </si>
-  <si>
-    <t>GRM155R61A823KA01D</t>
-  </si>
-  <si>
-    <t>24 nF</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>CAPC2013X94N</t>
-  </si>
-  <si>
-    <t>08051C243JAT2A</t>
-  </si>
-  <si>
-    <t>4.7 μF</t>
+    <t>1 μF</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C0402C104J4RACTU</t>
+  </si>
+  <si>
+    <t>C0402C105K9PACTU</t>
+  </si>
+  <si>
+    <t>Capacitor Polarised</t>
   </si>
   <si>
     <t>C7</t>
   </si>
   <si>
-    <t>CAPC1608X80N</t>
-  </si>
-  <si>
-    <t>C1608X6S1C475K080AC</t>
-  </si>
-  <si>
-    <t>56 μF</t>
-  </si>
-  <si>
-    <t>Capacitor Polarised</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>16SVF82M</t>
-  </si>
-  <si>
-    <t>20SVPF56MX</t>
+    <t>CAPPM3528X210N</t>
+  </si>
+  <si>
+    <t>293D106X9016B2TE3</t>
+  </si>
+  <si>
+    <t>100 μF</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>GRM31x</t>
+  </si>
+  <si>
+    <t>GRM31CD80J107MEA8K</t>
+  </si>
+  <si>
+    <t>220 pF</t>
+  </si>
+  <si>
+    <t>C11, C12</t>
+  </si>
+  <si>
+    <t>GRM033D70J224ME01D</t>
+  </si>
+  <si>
+    <t>GRM033R71C221KA01D</t>
   </si>
   <si>
     <t>22 μF</t>
   </si>
   <si>
-    <t>C9, C15, C16, C17</t>
-  </si>
-  <si>
-    <t>CAPC3225X270N</t>
-  </si>
-  <si>
-    <t>GRM32ER61E226KE15K</t>
-  </si>
-  <si>
-    <t>C10, C11, C12, C18</t>
-  </si>
-  <si>
-    <t>CL05B104KA5NNNC</t>
-  </si>
-  <si>
-    <t>27 μF</t>
-  </si>
-  <si>
-    <t>C13, C14</t>
-  </si>
-  <si>
-    <t>25SVPF27MX</t>
-  </si>
-  <si>
-    <t>C20, C21</t>
+    <t>C15, C16</t>
   </si>
   <si>
     <t>CAPC3216X180N</t>
@@ -191,43 +182,76 @@
     <t>CL31B226KPHNNNE</t>
   </si>
   <si>
-    <t>SSB44-M3_5BT</t>
-  </si>
-  <si>
-    <t>Schottky Diode</t>
+    <t>SMBJ18CA</t>
+  </si>
+  <si>
+    <t>TVS Diode (Bi-directional)</t>
   </si>
   <si>
     <t>D1</t>
   </si>
   <si>
-    <t>DIOM5436X244N</t>
-  </si>
-  <si>
-    <t>B2B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN HEADER VERT 2POS 2.5MM</t>
-  </si>
-  <si>
-    <t>DRML, DRMR, PROP, SOL, STMB, STMP, SW</t>
-  </si>
-  <si>
-    <t>FP-B2B-XH-A_LF_SN-MFG</t>
-  </si>
-  <si>
-    <t>CMP-2000-05888-3</t>
+    <t>DIOM5436X261N</t>
+  </si>
+  <si>
+    <t>PAM8302AASCR</t>
+  </si>
+  <si>
+    <t>DAMP</t>
+  </si>
+  <si>
+    <t>SOP65P490X110-8N</t>
   </si>
   <si>
     <t>DRV8847PWPR</t>
   </si>
   <si>
-    <t>DRV1, DRV2</t>
+    <t>DRV</t>
   </si>
   <si>
     <t>SOP65P640X120-17N</t>
   </si>
   <si>
-    <t>4.7 μH</t>
+    <t>61300411821</t>
+  </si>
+  <si>
+    <t>THT Vertical Socket Header WR-PHD, Pitch 2.54 mm, Single Row, 4 pins</t>
+  </si>
+  <si>
+    <t>ENC</t>
+  </si>
+  <si>
+    <t>CMP-1502-01316-4</t>
+  </si>
+  <si>
+    <t>MPZ1608S221ATA00</t>
+  </si>
+  <si>
+    <t>Power line Ferrite Bead 220Ω @ 100MHz 2.2A DCR 0.05Ω SMD 0603</t>
+  </si>
+  <si>
+    <t>FB1, FB2</t>
+  </si>
+  <si>
+    <t>FP-MPZ1608-0_8-MFG</t>
+  </si>
+  <si>
+    <t>CMP-08257-000028-1</t>
+  </si>
+  <si>
+    <t>AD623ARZ-R7</t>
+  </si>
+  <si>
+    <t>IAMP</t>
+  </si>
+  <si>
+    <t>SOIC127P600X175-8N</t>
+  </si>
+  <si>
+    <t>AD623AR-REEL7</t>
+  </si>
+  <si>
+    <t>1 μH</t>
   </si>
   <si>
     <t>Inductor</t>
@@ -236,21 +260,24 @@
     <t>L1</t>
   </si>
   <si>
-    <t>INDPM6664X610N</t>
-  </si>
-  <si>
-    <t>74439346047</t>
-  </si>
-  <si>
-    <t>1 μH</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
     <t>74438357010</t>
   </si>
   <si>
+    <t>B3B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 3POS 2.5MM</t>
+  </si>
+  <si>
+    <t>LEDA, SVOB, SVOP, SVOS</t>
+  </si>
+  <si>
+    <t>FP-B3B-XH-A_LF_SN-MFG</t>
+  </si>
+  <si>
+    <t>CMP-17439-000014-3</t>
+  </si>
+  <si>
     <t>Feather RP2040 Adalogger</t>
   </si>
   <si>
@@ -263,97 +290,106 @@
     <t>2796</t>
   </si>
   <si>
-    <t>DMN6075S-7</t>
-  </si>
-  <si>
-    <t>MOSFET (N-Channel)</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>SOT96P240X110-3N</t>
-  </si>
-  <si>
-    <t>DMN6075SQ-7</t>
-  </si>
-  <si>
-    <t>110 mΩ</t>
+    <t>100 mΩ</t>
   </si>
   <si>
     <t>Resistor</t>
   </si>
   <si>
-    <t>R1, R4</t>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>RESC2013X65N</t>
+  </si>
+  <si>
+    <t>RCWE0805R100FKEA</t>
+  </si>
+  <si>
+    <t>400 Ω</t>
+  </si>
+  <si>
+    <t>R2, R3</t>
+  </si>
+  <si>
+    <t>RESC1608X46N</t>
+  </si>
+  <si>
+    <t>PAT0603E4000BST1</t>
+  </si>
+  <si>
+    <t>680 mΩ</t>
+  </si>
+  <si>
+    <t>R4, R5</t>
   </si>
   <si>
     <t>ERJ6_B_BW_R_LW_CW_D</t>
   </si>
   <si>
-    <t>ERJ-6DSFR11V</t>
-  </si>
-  <si>
-    <t>680 mΩ</t>
-  </si>
-  <si>
-    <t>R2, R5</t>
-  </si>
-  <si>
     <t>ERJ-6DQJR68V</t>
   </si>
   <si>
     <t>10 kΩ</t>
   </si>
   <si>
-    <t>R3, R6, R10</t>
-  </si>
-  <si>
-    <t>RESC2012X70N</t>
-  </si>
-  <si>
-    <t>ERJ-6GEYJ103V</t>
-  </si>
-  <si>
-    <t>4.7 kΩ</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>RESAD1530W60L610D230</t>
-  </si>
-  <si>
-    <t>CF1_4C472J</t>
-  </si>
-  <si>
-    <t>301 Ω</t>
+    <t>R6, R7</t>
+  </si>
+  <si>
+    <t>RESC1005X40N</t>
+  </si>
+  <si>
+    <t>RC0402JR-0710KL</t>
+  </si>
+  <si>
+    <t>200 kΩ</t>
   </si>
   <si>
     <t>R8</t>
   </si>
   <si>
-    <t>RESC1005X40N</t>
-  </si>
-  <si>
-    <t>CRCW0402301RFKED</t>
-  </si>
-  <si>
-    <t>49.9 kΩ</t>
+    <t>ERA6AEB101V</t>
+  </si>
+  <si>
+    <t>ERA-6AEB204V</t>
+  </si>
+  <si>
+    <t>330 Ω</t>
   </si>
   <si>
     <t>R9</t>
   </si>
   <si>
-    <t>ERJ2RKD1004X</t>
-  </si>
-  <si>
-    <t>ERJ-2RKF4992X</t>
+    <t>RC0402FR-07330RL</t>
+  </si>
+  <si>
+    <t>5 kΩ</t>
+  </si>
+  <si>
+    <t>R10, R11, R13</t>
+  </si>
+  <si>
+    <t>RESC0603X26N</t>
+  </si>
+  <si>
+    <t>TNPW02015K00BEED</t>
+  </si>
+  <si>
+    <t>150 Ω</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>RESC2012X60N</t>
+  </si>
+  <si>
+    <t>RK73B2ATTD151J</t>
   </si>
   <si>
     <t>100 kΩ</t>
   </si>
   <si>
-    <t>R11</t>
+    <t>R14</t>
   </si>
   <si>
     <t>ERJ8ENF1000V</t>
@@ -365,37 +401,34 @@
     <t>732 kΩ</t>
   </si>
   <si>
-    <t>R12</t>
+    <t>R15</t>
   </si>
   <si>
     <t>ERJ-8ENF7323V</t>
   </si>
   <si>
-    <t>B3B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN HEADER VERT 3POS 2.5MM</t>
-  </si>
-  <si>
-    <t>SVOB, SVOP, TMP</t>
-  </si>
-  <si>
-    <t>FP-B3B-XH-A_LF_SN-MFG</t>
-  </si>
-  <si>
-    <t>CMP-17439-000014-3</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Boards</t>
+    <t>CS326</t>
+  </si>
+  <si>
+    <t>Relay or Contactor</t>
+  </si>
+  <si>
+    <t>SSR</t>
+  </si>
+  <si>
+    <t>SOP254P1030X390-8N</t>
+  </si>
+  <si>
+    <t>INA219BIDR</t>
+  </si>
+  <si>
+    <t>VAM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -457,9 +490,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{0EF9EE6F-4735-4533-8222-9EDEA1268861}"/>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -787,14 +818,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F29A72-50C2-4BC0-A284-E1CCECBBF6C2}">
-  <dimension ref="A1:H29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCEFBE8D-C481-435D-9AF0-F3D6748809DF}">
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="6" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -813,14 +844,8 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -831,7 +856,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -839,660 +864,605 @@
       <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="G2" s="1">
-        <f>F2*$H$2</f>
-        <v>5</v>
-      </c>
-      <c r="H2" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
-        <f t="shared" ref="G3:G29" si="0">F3*$H$2</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1">
         <v>2</v>
       </c>
-      <c r="G4" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="1">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="1">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1">
-        <v>4</v>
-      </c>
-      <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" s="1">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F13" s="1">
-        <v>2</v>
-      </c>
-      <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
       </c>
-      <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F15" s="1">
-        <v>7</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
       </c>
-      <c r="G18" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
       </c>
-      <c r="G20" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F21" s="1">
-        <v>2</v>
-      </c>
-      <c r="G21" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F22" s="1">
         <v>2</v>
       </c>
-      <c r="G22" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="1">
         <v>3</v>
       </c>
-      <c r="G23" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F28" s="1">
         <v>1</v>
       </c>
-      <c r="G28" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F29" s="1">
-        <v>3</v>
-      </c>
-      <c r="G29" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
